--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-dicom.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-dicom.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1067,28 +1067,31 @@
     <t>Précision topographique</t>
   </si>
   <si>
+    <t>Extension permettant d’associer à un code une précision (qualifier).</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:qualifier.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:qualifier.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:qualifier.extension:name</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
     <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:qualifier.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:qualifier.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension:qualifier.extension:name</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>Observation.bodySite.extension:qualifier.extension:name.id</t>
@@ -6040,7 +6043,7 @@
         <v>343</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6126,10 +6129,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6244,10 +6247,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6276,7 +6279,7 @@
         <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6362,10 +6365,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6391,13 +6394,13 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6447,7 +6450,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>93</v>
@@ -6482,10 +6485,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6511,10 +6514,10 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6565,7 +6568,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6600,10 +6603,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6718,10 +6721,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6838,10 +6841,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6864,19 +6867,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6925,7 +6928,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6946,10 +6949,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6960,10 +6963,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7078,10 +7081,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7198,10 +7201,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7227,16 +7230,16 @@
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7246,7 +7249,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7285,7 +7288,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7306,10 +7309,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7320,10 +7323,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7349,13 +7352,13 @@
         <v>321</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7405,7 +7408,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7426,10 +7429,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7440,10 +7443,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7469,14 +7472,14 @@
         <v>113</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7486,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7525,7 +7528,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7546,10 +7549,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7560,10 +7563,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7589,14 +7592,14 @@
         <v>321</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7606,7 +7609,7 @@
         <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>82</v>
@@ -7645,7 +7648,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7666,10 +7669,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7680,10 +7683,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7706,19 +7709,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7767,7 +7770,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7788,10 +7791,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7802,10 +7805,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7831,16 +7834,16 @@
         <v>321</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7889,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7910,10 +7913,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7924,7 +7927,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>340</v>
@@ -7955,10 +7958,10 @@
         <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8044,10 +8047,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8162,10 +8165,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8194,7 +8197,7 @@
         <v>343</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8280,10 +8283,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8309,13 +8312,13 @@
         <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8365,7 +8368,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>93</v>
@@ -8400,10 +8403,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8429,10 +8432,10 @@
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8463,7 +8466,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8481,7 +8484,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8519,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8545,13 +8548,13 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8559,7 +8562,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8601,7 +8604,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>93</v>
@@ -8636,10 +8639,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8662,13 +8665,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8719,7 +8722,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8754,10 +8757,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8780,19 +8783,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8841,7 +8844,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8862,10 +8865,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8876,10 +8879,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8905,16 +8908,16 @@
         <v>321</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8963,7 +8966,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8984,10 +8987,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8998,10 +9001,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9027,16 +9030,16 @@
         <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9064,10 +9067,10 @@
         <v>206</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9085,7 +9088,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9106,10 +9109,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9120,10 +9123,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9146,16 +9149,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9205,7 +9208,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9223,27 +9226,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9266,16 +9269,16 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9325,7 +9328,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9343,27 +9346,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9386,19 +9389,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9447,7 +9450,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9459,7 +9462,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9468,10 +9471,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9482,10 +9485,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9600,10 +9603,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9720,14 +9723,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9749,10 +9752,10 @@
         <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>142</v>
@@ -9807,7 +9810,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9842,10 +9845,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9868,13 +9871,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9925,7 +9928,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9934,7 +9937,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -9946,10 +9949,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9960,10 +9963,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9986,13 +9989,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10043,7 +10046,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10052,7 +10055,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10064,10 +10067,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10078,10 +10081,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10107,16 +10110,16 @@
         <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10144,10 +10147,10 @@
         <v>117</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10165,7 +10168,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10183,10 +10186,10 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>301</v>
@@ -10200,10 +10203,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10229,16 +10232,16 @@
         <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10266,10 +10269,10 @@
         <v>206</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10287,7 +10290,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10305,10 +10308,10 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>301</v>
@@ -10322,10 +10325,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10348,17 +10351,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10407,7 +10410,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10431,7 +10434,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10442,10 +10445,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10471,10 +10474,10 @@
         <v>321</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10525,7 +10528,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10546,10 +10549,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10560,10 +10563,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10586,16 +10589,16 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10645,7 +10648,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10666,10 +10669,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10680,10 +10683,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10706,16 +10709,16 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10765,7 +10768,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10786,10 +10789,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10800,10 +10803,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10826,19 +10829,19 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10887,7 +10890,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10908,10 +10911,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10922,10 +10925,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11040,10 +11043,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11160,14 +11163,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11189,10 +11192,10 @@
         <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>142</v>
@@ -11247,7 +11250,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11282,10 +11285,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11311,13 +11314,13 @@
         <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>205</v>
@@ -11369,7 +11372,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>93</v>
@@ -11387,7 +11390,7 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>211</v>
@@ -11404,10 +11407,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11433,13 +11436,13 @@
         <v>271</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>273</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O78" t="s" s="2">
         <v>275</v>
@@ -11491,7 +11494,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11509,7 +11512,7 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>278</v>
@@ -11526,10 +11529,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11555,13 +11558,13 @@
         <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>285</v>
@@ -11613,7 +11616,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11648,10 +11651,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11735,7 +11738,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11770,10 +11773,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11799,16 +11802,16 @@
         <v>83</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11857,7 +11860,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11878,10 +11881,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
